--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -81,24 +81,24 @@
     <t xml:space="preserve">Renca</t>
   </si>
   <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
@@ -108,12 +108,12 @@
     <t xml:space="preserve">Pudahuel</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:30</t>
+    <t xml:space="preserve">2026-09-09 23:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13121</v>
+        <v>13602</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2024</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13602</v>
+        <v>13121</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2024</v>
@@ -954,7 +954,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13122</v>
+        <v>13401</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2024</v>
@@ -971,7 +971,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13401</v>
+        <v>13122</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2024</v>
@@ -1039,7 +1039,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13129</v>
+        <v>13102</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2024</v>
@@ -1056,7 +1056,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13102</v>
+        <v>13129</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:27</t>
+    <t xml:space="preserve">2026-09-17 14:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -81,24 +81,24 @@
     <t xml:space="preserve">Renca</t>
   </si>
   <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
@@ -171,12 +171,12 @@
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Barnechea</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:22</t>
+    <t xml:space="preserve">2026-09-23 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13602</v>
+        <v>13121</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2024</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13121</v>
+        <v>13602</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2024</v>
@@ -954,7 +954,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13401</v>
+        <v>13122</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2024</v>
@@ -971,7 +971,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13122</v>
+        <v>13401</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2024</v>
@@ -1396,7 +1396,7 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13130</v>
+        <v>13113</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2024</v>
@@ -1413,7 +1413,7 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13113</v>
+        <v>13130</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:50</t>
+    <t xml:space="preserve">2026-10-01 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1581,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:13</t>
+    <t xml:space="preserve">2026-10-02 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:23</t>
+    <t xml:space="preserve">2026-10-02 15:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:09</t>
+    <t xml:space="preserve">2026-10-05 12:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
